--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -161,6 +161,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -373,11 +374,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -405,6 +418,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -419,6 +433,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -836,7 +851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-09-29 (3 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-09-30 (4 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -919,10 +934,10 @@
         <v>46266</v>
       </c>
       <c r="B2" t="n">
-        <v>232.217</v>
+        <v>303.49</v>
       </c>
       <c r="C2" t="n">
-        <v>8.018000000000001</v>
+        <v>10.828</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -937,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>67.96799999999999</v>
+        <v>92.752</v>
       </c>
     </row>
   </sheetData>
@@ -952,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1060,26 @@
       </c>
       <c r="F4" t="n">
         <v>103194</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B5" t="n">
+        <v>71273</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23864</v>
+      </c>
+      <c r="E5" t="n">
+        <v>920</v>
+      </c>
+      <c r="F5" t="n">
+        <v>98867</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,6 +1230,35 @@
         <v>133</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98975</v>
+      </c>
+      <c r="C5" t="n">
+        <v>71273</v>
+      </c>
+      <c r="D5" t="n">
+        <v>26674</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23864</v>
+      </c>
+      <c r="G5" t="n">
+        <v>920</v>
+      </c>
+      <c r="H5" t="n">
+        <v>107</v>
+      </c>
+      <c r="I5" t="n">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -156,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Ecuador power generation by type (CENACE) (to Sep/26)</a:t>
+              <a:t>Ecuador power generation by type (CENACE) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2</f>
+              <f>'Chart'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2</f>
+              <f>'Chart'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2</f>
+              <f>'Chart'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2</f>
+              <f>'Chart'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2</f>
+              <f>'Chart'!$F$2:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -326,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2</f>
+              <f>'Chart'!$G$2:$G$3</f>
             </numRef>
           </val>
         </ser>
@@ -354,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2</f>
+              <f>'Chart'!$H$2:$H$3</f>
             </numRef>
           </val>
         </ser>
@@ -851,7 +851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-09-30 (4 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-01 (5 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -953,6 +953,32 @@
       </c>
       <c r="H2" t="n">
         <v>92.752</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B3" t="n">
+        <v>73.375</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.794</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25.409</v>
       </c>
     </row>
   </sheetData>
@@ -967,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,6 +1106,26 @@
       </c>
       <c r="F5" t="n">
         <v>98867</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>73375</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2794</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24825</v>
+      </c>
+      <c r="E6" t="n">
+        <v>584</v>
+      </c>
+      <c r="F6" t="n">
+        <v>101578</v>
       </c>
     </row>
   </sheetData>
@@ -1093,7 +1139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1259,6 +1305,35 @@
         <v>96</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101684</v>
+      </c>
+      <c r="C6" t="n">
+        <v>73375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>27619</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2794</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24825</v>
+      </c>
+      <c r="G6" t="n">
+        <v>584</v>
+      </c>
+      <c r="H6" t="n">
+        <v>105</v>
+      </c>
+      <c r="I6" t="n">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -797,7 +798,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -840,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -855,7 +854,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
@@ -930,7 +928,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B2" t="n">
@@ -956,7 +954,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B3" t="n">

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -798,6 +797,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -840,6 +840,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -854,6 +855,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
@@ -928,7 +930,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B2" t="n">
@@ -954,7 +956,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B3" t="n">

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -851,7 +851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-01 (5 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-02 (6 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -960,10 +960,10 @@
         <v>46296</v>
       </c>
       <c r="B3" t="n">
-        <v>73.375</v>
+        <v>140.83</v>
       </c>
       <c r="C3" t="n">
-        <v>2.794</v>
+        <v>5.573</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>25.409</v>
+        <v>50.864</v>
       </c>
     </row>
   </sheetData>
@@ -993,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,6 +1126,26 @@
       </c>
       <c r="F6" t="n">
         <v>101578</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B7" t="n">
+        <v>67455</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2779</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24855</v>
+      </c>
+      <c r="E7" t="n">
+        <v>600</v>
+      </c>
+      <c r="F7" t="n">
+        <v>95689</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1334,6 +1354,35 @@
         <v>88</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95778</v>
+      </c>
+      <c r="C7" t="n">
+        <v>67455</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27634</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24855</v>
+      </c>
+      <c r="G7" t="n">
+        <v>600</v>
+      </c>
+      <c r="H7" t="n">
+        <v>89</v>
+      </c>
+      <c r="I7" t="n">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CENACE raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Daily" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CENACE raw" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,11 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -142,336 +138,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Ecuador power generation by type (CENACE) (to Oct/26)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$B$2:$B$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EB6834"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$C$2:$C$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!D1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$D$2:$D$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EDA100"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$E$2:$E$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!F1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$F$2:$F$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!G1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="008300"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$G$2:$G$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!H1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="9A9A9A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$H$2:$H$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="30"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="low"/>
-        <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr/>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>GWh per month</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-      <spPr>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="10080000" cy="4680000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -881,118 +547,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Coal</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B2" t="n">
-        <v>303.49</v>
-      </c>
-      <c r="C2" t="n">
-        <v>10.828</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>92.752</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B3" t="n">
-        <v>140.83</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5.573</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>50.864</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1029,7 +583,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="3" t="n">
         <v>46291</v>
       </c>
       <c r="B2" t="n">
@@ -1049,7 +603,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>46293</v>
       </c>
       <c r="B3" t="n">
@@ -1069,7 +623,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="3" t="n">
         <v>46294</v>
       </c>
       <c r="B4" t="n">
@@ -1089,7 +643,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="3" t="n">
         <v>46295</v>
       </c>
       <c r="B5" t="n">
@@ -1109,7 +663,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B6" t="n">
@@ -1129,7 +683,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="3" t="n">
         <v>46297</v>
       </c>
       <c r="B7" t="n">
@@ -1153,7 +707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1210,7 +764,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="3" t="n">
         <v>46291</v>
       </c>
       <c r="B2" t="n">
@@ -1239,7 +793,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>46293</v>
       </c>
       <c r="B3" t="n">
@@ -1268,7 +822,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="3" t="n">
         <v>46294</v>
       </c>
       <c r="B4" t="n">
@@ -1297,7 +851,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="3" t="n">
         <v>46295</v>
       </c>
       <c r="B5" t="n">
@@ -1326,7 +880,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B6" t="n">
@@ -1355,7 +909,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="3" t="n">
         <v>46297</v>
       </c>
       <c r="B7" t="n">

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -517,7 +517,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-02 (6 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-03 (7 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,26 @@
       </c>
       <c r="F7" t="n">
         <v>95689</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B8" t="n">
+        <v>65572</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2843</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24045</v>
+      </c>
+      <c r="E8" t="n">
+        <v>568</v>
+      </c>
+      <c r="F8" t="n">
+        <v>93028</v>
       </c>
     </row>
   </sheetData>
@@ -713,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,6 +957,35 @@
         <v>91</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93081</v>
+      </c>
+      <c r="C8" t="n">
+        <v>65572</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26888</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2843</v>
+      </c>
+      <c r="F8" t="n">
+        <v>24045</v>
+      </c>
+      <c r="G8" t="n">
+        <v>568</v>
+      </c>
+      <c r="H8" t="n">
+        <v>54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -517,7 +517,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-03 (7 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-05 (8 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,6 +720,26 @@
       </c>
       <c r="F8" t="n">
         <v>93028</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75717</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2822</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23371</v>
+      </c>
+      <c r="E9" t="n">
+        <v>643</v>
+      </c>
+      <c r="F9" t="n">
+        <v>102553</v>
       </c>
     </row>
   </sheetData>
@@ -733,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,6 +1006,35 @@
         <v>84</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102636</v>
+      </c>
+      <c r="C9" t="n">
+        <v>75717</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26193</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2822</v>
+      </c>
+      <c r="F9" t="n">
+        <v>23371</v>
+      </c>
+      <c r="G9" t="n">
+        <v>643</v>
+      </c>
+      <c r="H9" t="n">
+        <v>83</v>
+      </c>
+      <c r="I9" t="n">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -517,7 +517,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-05 (8 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-06 (9 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,26 @@
       </c>
       <c r="F9" t="n">
         <v>102553</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B10" t="n">
+        <v>77991</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2816</v>
+      </c>
+      <c r="D10" t="n">
+        <v>22541</v>
+      </c>
+      <c r="E10" t="n">
+        <v>567</v>
+      </c>
+      <c r="F10" t="n">
+        <v>103916</v>
       </c>
     </row>
   </sheetData>
@@ -753,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,6 +1055,35 @@
         <v>72</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103966</v>
+      </c>
+      <c r="C10" t="n">
+        <v>77991</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25358</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2816</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22541</v>
+      </c>
+      <c r="G10" t="n">
+        <v>567</v>
+      </c>
+      <c r="H10" t="n">
+        <v>51</v>
+      </c>
+      <c r="I10" t="n">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -517,7 +517,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-06 (9 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-07 (10 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,6 +760,26 @@
       </c>
       <c r="F10" t="n">
         <v>103916</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78817</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2781</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21329</v>
+      </c>
+      <c r="E11" t="n">
+        <v>632</v>
+      </c>
+      <c r="F11" t="n">
+        <v>103559</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1084,6 +1104,35 @@
         <v>79</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B11" t="n">
+        <v>103708</v>
+      </c>
+      <c r="C11" t="n">
+        <v>78817</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24110</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2781</v>
+      </c>
+      <c r="F11" t="n">
+        <v>21329</v>
+      </c>
+      <c r="G11" t="n">
+        <v>632</v>
+      </c>
+      <c r="H11" t="n">
+        <v>148</v>
+      </c>
+      <c r="I11" t="n">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -517,7 +517,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-07 (10 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-10 (11 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,26 @@
       </c>
       <c r="F11" t="n">
         <v>103559</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>72231</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1621</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18023</v>
+      </c>
+      <c r="E12" t="n">
+        <v>697</v>
+      </c>
+      <c r="F12" t="n">
+        <v>92572</v>
       </c>
     </row>
   </sheetData>
@@ -793,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,6 +1153,35 @@
         <v>101</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92681</v>
+      </c>
+      <c r="C12" t="n">
+        <v>72231</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19644</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1621</v>
+      </c>
+      <c r="F12" t="n">
+        <v>18023</v>
+      </c>
+      <c r="G12" t="n">
+        <v>697</v>
+      </c>
+      <c r="H12" t="n">
+        <v>109</v>
+      </c>
+      <c r="I12" t="n">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -463,7 +463,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -506,7 +505,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -521,7 +519,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -463,6 +463,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -505,6 +506,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -515,10 +517,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-10 (11 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
-        </is>
-      </c>
-    </row>
+          <t>2026-09-26 to 2026-10-26 (12 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
@@ -544,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +800,26 @@
       </c>
       <c r="F12" t="n">
         <v>92572</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B13" t="n">
+        <v>67536</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1514</v>
+      </c>
+      <c r="D13" t="n">
+        <v>25419</v>
+      </c>
+      <c r="E13" t="n">
+        <v>522</v>
+      </c>
+      <c r="F13" t="n">
+        <v>94991</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1179,6 +1202,35 @@
         <v>79</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95032</v>
+      </c>
+      <c r="C13" t="n">
+        <v>67536</v>
+      </c>
+      <c r="D13" t="n">
+        <v>26933</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1514</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25419</v>
+      </c>
+      <c r="G13" t="n">
+        <v>522</v>
+      </c>
+      <c r="H13" t="n">
+        <v>41</v>
+      </c>
+      <c r="I13" t="n">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -517,7 +517,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-26 (12 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-27 (13 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -820,6 +820,26 @@
       </c>
       <c r="F13" t="n">
         <v>94991</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B14" t="n">
+        <v>71940</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1641</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24810</v>
+      </c>
+      <c r="E14" t="n">
+        <v>498</v>
+      </c>
+      <c r="F14" t="n">
+        <v>98888</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,6 +1251,35 @@
         <v>118</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98923</v>
+      </c>
+      <c r="C14" t="n">
+        <v>71940</v>
+      </c>
+      <c r="D14" t="n">
+        <v>26450</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1641</v>
+      </c>
+      <c r="F14" t="n">
+        <v>24810</v>
+      </c>
+      <c r="G14" t="n">
+        <v>498</v>
+      </c>
+      <c r="H14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -517,7 +517,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-27 (13 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-28 (14 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,6 +840,26 @@
       </c>
       <c r="F14" t="n">
         <v>98888</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B15" t="n">
+        <v>67798</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1710</v>
+      </c>
+      <c r="D15" t="n">
+        <v>23954</v>
+      </c>
+      <c r="E15" t="n">
+        <v>442</v>
+      </c>
+      <c r="F15" t="n">
+        <v>93904</v>
       </c>
     </row>
   </sheetData>
@@ -853,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1280,6 +1300,35 @@
         <v>65</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B15" t="n">
+        <v>94014</v>
+      </c>
+      <c r="C15" t="n">
+        <v>67798</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25664</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1710</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23954</v>
+      </c>
+      <c r="G15" t="n">
+        <v>442</v>
+      </c>
+      <c r="H15" t="n">
+        <v>110</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_generation_daily.xlsx
@@ -517,7 +517,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 to 2026-10-28 (14 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
+          <t>2026-09-26 to 2026-10-29 (15 days). HISTORY IS LIMITED: CENACE publishes only the last complete day and keeps no public archive, so the series starts at the first run of ECUADOR_CENACE.py (2026-09-26) and cannot be backfilled to 2021. Days the page wasn't read are gaps.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,6 +860,26 @@
       </c>
       <c r="F15" t="n">
         <v>93904</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B16" t="n">
+        <v>69904</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2453</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25013</v>
+      </c>
+      <c r="E16" t="n">
+        <v>451</v>
+      </c>
+      <c r="F16" t="n">
+        <v>97821</v>
       </c>
     </row>
   </sheetData>
@@ -873,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1349,35 @@
         <v>100</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97881</v>
+      </c>
+      <c r="C16" t="n">
+        <v>69904</v>
+      </c>
+      <c r="D16" t="n">
+        <v>27466</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2453</v>
+      </c>
+      <c r="F16" t="n">
+        <v>25013</v>
+      </c>
+      <c r="G16" t="n">
+        <v>451</v>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
